--- a/pacjenci/JUSTYNA GARA.xlsx
+++ b/pacjenci/JUSTYNA GARA.xlsx
@@ -413,323 +413,242 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>26.09.2022</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Ziarnica złośliwa. Ocena zaawansowania.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 62min od podania 18F-FDG. Glikemia: 115mg%</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Miernie zwiększony metabolizm FDG w przysadce - do oceny klinicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Płyn w obu jamach opłucnowych grubości płaszcza do 42mm. Wkłucie centralne założone do żyły szyjnej wewnętrznej po stronie prawej.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Balon cewnika w pęcherzu moczowym. Cewnik w prawej żyle biodrowej  zewnętrznej. Liczne poziomy płynów w jelitach - stan podniedrożnościowy. Płyn w prawym zachyłku przyokrężniczym, płyn w lewym zachyłku przy okrężniczym w mniejszej ilości.  Układ kostny: Rozlanie zwiększony metabolizm FDG w układzie kostnym, SUV max do 11,0.  Inny: Miernie zwiększony metabolizm w topografii nieco pogrubiałej skórze pośladków, SUV max 2,7 - do oceny klinicznej. Zwiększony metabolizm FDG w topografii przyczepów mięśni pośladkowych małych, SUV max do 6,3 - w pierwszej kolejności zmiany przeciążeniowe.  Wartości referencyjne: MBPS SUVmax 1,6, Prawy płat wątroby SUVmax do 2,5.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono rozlanie zwiększony wychwyt znacznika w układzie kostnym - do weryfikacji w trepanobiopsji. Poza tym nie uwidoczniono jednoznacznych cech aktywnej choroby chłoniakowej.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>11</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>01.12.2022</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Ziarnica złośliwa. Wczesna ocena odpowiedzi po 2 cyklach ABVD.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 74min od podania 18F-FDG. Glikemia: 83mg%</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Miernie zwiększony metabolizm FDG w przysadce - do oceny klinicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Aktywny metabolicznie obszar w śródpiersiu przednim pośrodkowo powyżej żyły bezimiennej wielkości 8mm wg PET, SUV max do 4,1. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia.  Brzuch i miednica: Pobudzenie metaboliczne n w miednicy po stronie lewej w łączności z lewymi przydatkami SUV max 6,3 [Im fuz 241] Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym- do kontroli.  Inny: Asymetryczne pobudzenie metaboliczne w mięśniach szyi po stronie prawej- zmiany przeciążeniowe. Pobudzenie metaboliczne i zwiększona aktywność metaboliczna w topografii tkanki brunatnej szyi i KLP i pojedynczy obszar w jamie brzusznej z obecnością drobnych węzłów chłonnych na szyi wielkości do 5mm, SUV max do 1,9- do kontroli.    Wartości referencyjne: MBPS SUVmax 1,9 Prawy płat wątroby SUVmax do 3,0.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywny metabolicznie obszar w środpiersiu przednim - do weryfikacji. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>6.3</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>26.01.2023</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Badanie kontrolne po IV cyklu ChTh.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 60 min od podania 18F-FDG. Glikemia: 72 mg%</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Znaczna hypoplazja zatok czołowych.  Klatka piersiowa i śródpiersie: Utrzymuje się aktywny metabolicznie obszar w śródpiersiu przednim pośrodkowo powyżej żyły bezimiennej, średnicy 8 mm wg PET SUV max do 3,7 [Im fuz. 103]. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste nadprzeponowo w płucu lewym.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielka ilość płynu w jamie Douglasa po stronie lewej.  Układ kostny: Rozlanie wzmożony metabolizm FDG w układzie kostnym objętym badaniem- w pierwszej kolejności związany z prowadzonym leczeniem. Niewielka esowata skolioza kręgosłupa: prawowypukła w odcinku piersiowym oraz lewowypukła w odcinku piersiowym, z rotacją kręgów.  Os sacrum arcuatum. Odszczepione jądra kostnienia w okolicy spojenia łonowego obustronnie lub zmiany pourazowe.  Inny: Pobudzenie metaboliczne w mięśniach szyi i kończyn górnych - w pierwszej kolejności zmiany przeciążeniowo-odczynowe.  Wartości referencyjne: MBPS SUVmax 1,3; Prawy płat wątroby SUVmax do 2,7.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność nadal aktywnego metabolicznie drobnego obszaru w śródpiersiu przednim pośrodkowo - do weryfikacji. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>3.7</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>23.03.2023</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Badanie kontrolne po IV cyklu ChTh.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 53 min od podania 18F-FDG. Glikemia: 83 mg%.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Znaczna hypoplazja zatok czołowych.  Klatka piersiowa i śródpiersie: Nadal utrzymuje się aktywny metabolicznie obszar w śródpiersiu przednim pośrodkowo powyżej żyły bezimiennej, średnicy 8 mm wg PET SUV max do 3,8 [Im fuz. 102] - do oceny w badaniu TK KLP z kontrastem dożylnym/weryfikacji. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste nadprzeponowo w płucu lewym.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nieliczne, drobne węzły chłonne krezkowe i przyaortalne, wielkości do 10x7mm. Niewielka ilość płynu w jamie Douglasa.  Układ kostny: Rozlanie wzmożony metabolizm FDG w układzie kostnym objętym badaniem- w pierwszej kolejności związany z prowadzonym leczeniem. Niewielka esowata skolioza kręgosłupa: prawowypukła w odcinku piersiowym oraz lewowypukła w odcinku piersiowym, z rotacją kręgów.  Os sacrum arcuatum. Odszczepione jądra kostnienia w okolicy spojenia łonowego obustronnie lub zmiany pourazowe.  Wartości referencyjne: MBPS SUVmax 1,7; Prawy płat wątroby SUVmax do 3,6.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność nadal aktywnego metabolicznie drobnego obszaru w śródpiersiu przednim pośrodkowo - do weryfikacji, jak w badaniach poprzednich. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>3.8</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>24.07.2023</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Badanie odpowiedzi po zakończeniu leczenia- po VI cyklach ABVD.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 56 min od podania 18F-FDG. Glikemia: 93 mg%.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Miernie pobudzone metabolicznie węzły chłonne przedziału 2 obustronnie wielkości do 11mm, SUV max do 3,1- do kontroli. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Znaczna hypoplazja zatok czołowych.  Klatka piersiowa i śródpiersie: Nadal utrzymuje się aktywny metabolicznie obszar w śródpiersiu przednim pośrodkowo powyżej żyły bezimiennej, średnicy 10 mm wg PET SUV max do 6,1 [Im fuz. 102]. Pobudzony metabolicznie węzeł chłonny przytchawiczy górny prawy wielkości 12x9mm, SUV max 3,8- do kontroli. Masa miękkotkankowa w śródpiersiu, zamostkowo, pośrodkowo i po stronie lewej, wielkości ok.  62x34x58mm wg PET, SUV max 5,2. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste nadprzeponowo w płucu lewym.  Brzuch i miednica: Odcinkowe pobudzenie metaboliczne w topografii pętli jelitowych- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nieliczne, drobne węzły chłonne krezkowe i przyaortalne, wielkości do 9x6mm.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Niewielka esowata skolioza kręgosłupa: prawowypukła w odcinku piersiowym oraz lewowypukła w odcinku piersiowym, z rotacją kręgów.  Os sacrum arcuatum. Odszczepione jądra kostnienia w okolicy spojenia łonowego obustronnie lub zmiany pourazowe.  Wartości referencyjne: MBPS SUVmax do 2,6; Prawy płat wątroby SUVmax do 3,9.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność nadal aktywnego metabolicznie drobnego obszaru w śródpiersiu przednim pośrodkowo a także pobudzonego metabolicznie węzła chłonnego przytchawiczego - wymaga kontroli. W obecnym badaniu widoczna jest ponadto niejednorodna, częściowo rozfragmentowana masa miękkotkankowa w śródpiersiu - podejrzenie wznowy.  Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>6.1</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>01.02.2024</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>6</v>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Ocena remisji chłoniaka.</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 94 mg%.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Znaczna hypoplazja zatok czołowych.  Klatka piersiowa i śródpiersie: Nadal utrzymuje się aktywny metabolicznie obszar w śródpiersiu przednim pośrodkowo powyżej żyły bezimiennej, wielkości  9mm wg PET SUV max do 5,2 [Im fuz. 100] oraz w topografii węzłów chłonnych przytchawiczych dolnych prawych, SUV max 4,1. Pobudzony metabolicznie węzeł chłonny przytchawiczy górny prawy wielkości 14x11mm, SUV max 4,0- do kontroli. Niejednorodnie aktywna metabolicznie masa miękkotkankowa w śródpiersiu, zamostkowo, pośrodkowo i po stronie lewej, o orientacyjnych wymiarach:.  62x23x50mm wg PET, SUV max 4,4- dokładna ocena wielkości masy mozliwa w badaniu TK KLP z kntrastem dozylnym. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste nadprzeponowo w płucu lewym.  Brzuch i miednica: Pobudzenie metaboliczne części wpustowej żołądka- czynnościowo? Odcinkowe pobudzenie metaboliczne w topografii pętli jelitowych- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Niewielka esowata skolioza kręgosłupa: prawowypukła w odcinku piersiowym oraz lewowypukła w odcinku piersiowym, z rotacją kręgów.  Os sacrum arcuatum. Odszczepione jądra kostnienia w okolicy spojenia łonowego obustronnie lub zmiany pourazowe.  Wartości referencyjne: MBPS SUVmax do 1,9; Prawy płat wątroby SUVmax do 3,3.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność nadal aktywnego metabolicznie drobnego obszaru w śródpiersiu przednim pośrodkowo a także pobudzonego metabolicznie węzła chłonnego przytchawiczego - wymaga kontroli. Ponadto widoczna jest niejednorodna, częściowo rozfragmentowana masa miękkotkankowa w śródpiersiu - 0braz bez istotnych zmian w stosunku do badania PET z 24.07.2023.  Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>5.2</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/JUSTYNA GARA.xlsx
+++ b/pacjenci/JUSTYNA GARA.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 62min od podania 18F-FDG. Glikemia: 115mg%</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Miernie zwiększony metabolizm FDG w przysadce - do oceny klinicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Płyn w obu jamach opłucnowych grubości płaszcza do 42mm. Wkłucie centralne założone do żyły szyjnej wewnętrznej po stronie prawej.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Balon cewnika w pęcherzu moczowym. Cewnik w prawej żyle biodrowej  zewnętrznej. Liczne poziomy płynów w jelitach - stan podniedrożnościowy. Płyn w prawym zachyłku przyokrężniczym, płyn w lewym zachyłku przy okrężniczym w mniejszej ilości.  Układ kostny: Rozlanie zwiększony metabolizm FDG w układzie kostnym, SUV max do 11,0.  Inny: Miernie zwiększony metabolizm w topografii nieco pogrubiałej skórze pośladków, SUV max 2,7 - do oceny klinicznej. Zwiększony metabolizm FDG w topografii przyczepów mięśni pośladkowych małych, SUV max do 6,3 - w pierwszej kolejności zmiany przeciążeniowe.  Wartości referencyjne: MBPS SUVmax 1,6, Prawy płat wątroby SUVmax do 2,5.</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Miernie zwiększony metabolizm FDG w przysadce - do oceny klinicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Płyn w obu jamach opłucnowych grubości płaszcza do 42mm. Wkłucie centralne założone do żyły szyjnej wewnętrznej po stronie prawej.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Balon cewnika w pęcherzu moczowym. Cewnik w prawej żyle biodrowej  zewnętrznej. Liczne poziomy płynów w jelitach - stan podniedrożnościowy. Płyn w prawym zachyłku przyokrężniczym, płyn w lewym zachyłku przy okrężniczym w mniejszej ilości.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Rozlanie zwiększony metabolizm FDG w układzie kostnym, SUV max do 11,0.  Inny: Miernie zwiększony metabolizm w topografii nieco pogrubiałej skórze pośladków, SUV max 2,7 - do oceny klinicznej. Zwiększony metabolizm FDG w topografii przyczepów mięśni pośladkowych małych, SUV max do 6,3 - w pierwszej kolejności zmiany przeciążeniowe.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono rozlanie zwiększony wychwyt znacznika w układzie kostnym - do weryfikacji w trepanobiopsji. Poza tym nie uwidoczniono jednoznacznych cech aktywnej choroby chłoniakowej.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>11</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 74min od podania 18F-FDG. Glikemia: 83mg%</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Miernie zwiększony metabolizm FDG w przysadce - do oceny klinicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Aktywny metabolicznie obszar w śródpiersiu przednim pośrodkowo powyżej żyły bezimiennej wielkości 8mm wg PET, SUV max do 4,1. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia.  Brzuch i miednica: Pobudzenie metaboliczne n w miednicy po stronie lewej w łączności z lewymi przydatkami SUV max 6,3 [Im fuz 241] Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym- do kontroli.  Inny: Asymetryczne pobudzenie metaboliczne w mięśniach szyi po stronie prawej- zmiany przeciążeniowe. Pobudzenie metaboliczne i zwiększona aktywność metaboliczna w topografii tkanki brunatnej szyi i KLP i pojedynczy obszar w jamie brzusznej z obecnością drobnych węzłów chłonnych na szyi wielkości do 5mm, SUV max do 1,9- do kontroli.    Wartości referencyjne: MBPS SUVmax 1,9 Prawy płat wątroby SUVmax do 3,0.</t>
+          <t>83</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Miernie zwiększony metabolizm FDG w przysadce - do oceny klinicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie obszar w śródpiersiu przednim pośrodkowo powyżej żyły bezimiennej wielkości 8mm wg PET, SUV max do 4,1. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne n w miednicy po stronie lewej w łączności z lewymi przydatkami SUV max 6,3 [Im fuz 241] Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Niejednorodny metabolizm FDG w układzie kostnym- do kontroli.  Inny: Asymetryczne pobudzenie metaboliczne w mięśniach szyi po stronie prawej- zmiany przeciążeniowe. Pobudzenie metaboliczne i zwiększona aktywność metaboliczna w topografii tkanki brunatnej szyi i KLP i pojedynczy obszar w jamie brzusznej z obecnością drobnych węzłów chłonnych na szyi wielkości do 5mm, SUV max do 1,9- do kontroli.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywny metabolicznie obszar w środpiersiu przednim - do weryfikacji. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>6.3</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 60 min od podania 18F-FDG. Glikemia: 72 mg%</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Znaczna hypoplazja zatok czołowych.  Klatka piersiowa i śródpiersie: Utrzymuje się aktywny metabolicznie obszar w śródpiersiu przednim pośrodkowo powyżej żyły bezimiennej, średnicy 8 mm wg PET SUV max do 3,7 [Im fuz. 103]. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste nadprzeponowo w płucu lewym.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielka ilość płynu w jamie Douglasa po stronie lewej.  Układ kostny: Rozlanie wzmożony metabolizm FDG w układzie kostnym objętym badaniem- w pierwszej kolejności związany z prowadzonym leczeniem. Niewielka esowata skolioza kręgosłupa: prawowypukła w odcinku piersiowym oraz lewowypukła w odcinku piersiowym, z rotacją kręgów.  Os sacrum arcuatum. Odszczepione jądra kostnienia w okolicy spojenia łonowego obustronnie lub zmiany pourazowe.  Inny: Pobudzenie metaboliczne w mięśniach szyi i kończyn górnych - w pierwszej kolejności zmiany przeciążeniowo-odczynowe.  Wartości referencyjne: MBPS SUVmax 1,3; Prawy płat wątroby SUVmax do 2,7.</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Znaczna hypoplazja zatok czołowych.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Utrzymuje się aktywny metabolicznie obszar w śródpiersiu przednim pośrodkowo powyżej żyły bezimiennej, średnicy 8 mm wg PET SUV max do 3,7 [Im fuz. 103]. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste nadprzeponowo w płucu lewym.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielka ilość płynu w jamie Douglasa po stronie lewej.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Rozlanie wzmożony metabolizm FDG w układzie kostnym objętym badaniem- w pierwszej kolejności związany z prowadzonym leczeniem. Niewielka esowata skolioza kręgosłupa: prawowypukła w odcinku piersiowym oraz lewowypukła w odcinku piersiowym, z rotacją kręgów.  Os sacrum arcuatum. Odszczepione jądra kostnienia w okolicy spojenia łonowego obustronnie lub zmiany pourazowe.  Inny: Pobudzenie metaboliczne w mięśniach szyi i kończyn górnych - w pierwszej kolejności zmiany przeciążeniowo-odczynowe.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność nadal aktywnego metabolicznie drobnego obszaru w śródpiersiu przednim pośrodkowo - do weryfikacji. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>3.7</v>
       </c>
     </row>
@@ -568,20 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 53 min od podania 18F-FDG. Glikemia: 83 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Znaczna hypoplazja zatok czołowych.  Klatka piersiowa i śródpiersie: Nadal utrzymuje się aktywny metabolicznie obszar w śródpiersiu przednim pośrodkowo powyżej żyły bezimiennej, średnicy 8 mm wg PET SUV max do 3,8 [Im fuz. 102] - do oceny w badaniu TK KLP z kontrastem dożylnym/weryfikacji. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste nadprzeponowo w płucu lewym.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nieliczne, drobne węzły chłonne krezkowe i przyaortalne, wielkości do 10x7mm. Niewielka ilość płynu w jamie Douglasa.  Układ kostny: Rozlanie wzmożony metabolizm FDG w układzie kostnym objętym badaniem- w pierwszej kolejności związany z prowadzonym leczeniem. Niewielka esowata skolioza kręgosłupa: prawowypukła w odcinku piersiowym oraz lewowypukła w odcinku piersiowym, z rotacją kręgów.  Os sacrum arcuatum. Odszczepione jądra kostnienia w okolicy spojenia łonowego obustronnie lub zmiany pourazowe.  Wartości referencyjne: MBPS SUVmax 1,7; Prawy płat wątroby SUVmax do 3,6.</t>
+          <t>83</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Znaczna hypoplazja zatok czołowych.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Nadal utrzymuje się aktywny metabolicznie obszar w śródpiersiu przednim pośrodkowo powyżej żyły bezimiennej, średnicy 8 mm wg PET SUV max do 3,8 [Im fuz. 102] - do oceny w badaniu TK KLP z kontrastem dożylnym/weryfikacji. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste nadprzeponowo w płucu lewym.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nieliczne, drobne węzły chłonne krezkowe i przyaortalne, wielkości do 10x7mm. Niewielka ilość płynu w jamie Douglasa.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Rozlanie wzmożony metabolizm FDG w układzie kostnym objętym badaniem- w pierwszej kolejności związany z prowadzonym leczeniem. Niewielka esowata skolioza kręgosłupa: prawowypukła w odcinku piersiowym oraz lewowypukła w odcinku piersiowym, z rotacją kręgów.  Os sacrum arcuatum. Odszczepione jądra kostnienia w okolicy spojenia łonowego obustronnie lub zmiany pourazowe.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność nadal aktywnego metabolicznie drobnego obszaru w śródpiersiu przednim pośrodkowo - do weryfikacji, jak w badaniach poprzednich. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="L5" t="n">
         <v>3.8</v>
       </c>
     </row>
@@ -601,20 +726,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 56 min od podania 18F-FDG. Glikemia: 93 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>: Miernie pobudzone metabolicznie węzły chłonne przedziału 2 obustronnie wielkości do 11mm, SUV max do 3,1- do kontroli. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Znaczna hypoplazja zatok czołowych.  Klatka piersiowa i śródpiersie: Nadal utrzymuje się aktywny metabolicznie obszar w śródpiersiu przednim pośrodkowo powyżej żyły bezimiennej, średnicy 10 mm wg PET SUV max do 6,1 [Im fuz. 102]. Pobudzony metabolicznie węzeł chłonny przytchawiczy górny prawy wielkości 12x9mm, SUV max 3,8- do kontroli. Masa miękkotkankowa w śródpiersiu, zamostkowo, pośrodkowo i po stronie lewej, wielkości ok.  62x34x58mm wg PET, SUV max 5,2. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste nadprzeponowo w płucu lewym.  Brzuch i miednica: Odcinkowe pobudzenie metaboliczne w topografii pętli jelitowych- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nieliczne, drobne węzły chłonne krezkowe i przyaortalne, wielkości do 9x6mm.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Niewielka esowata skolioza kręgosłupa: prawowypukła w odcinku piersiowym oraz lewowypukła w odcinku piersiowym, z rotacją kręgów.  Os sacrum arcuatum. Odszczepione jądra kostnienia w okolicy spojenia łonowego obustronnie lub zmiany pourazowe.  Wartości referencyjne: MBPS SUVmax do 2,6; Prawy płat wątroby SUVmax do 3,9.</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Miernie pobudzone metabolicznie węzły chłonne przedziału 2 obustronnie wielkości do 11mm, SUV max do 3,1- do kontroli. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Znaczna hypoplazja zatok czołowych.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Nadal utrzymuje się aktywny metabolicznie obszar w śródpiersiu przednim pośrodkowo powyżej żyły bezimiennej, średnicy 10 mm wg PET SUV max do 6,1 [Im fuz. 102]. Pobudzony metabolicznie węzeł chłonny przytchawiczy górny prawy wielkości 12x9mm, SUV max 3,8- do kontroli. Masa miękkotkankowa w śródpiersiu, zamostkowo, pośrodkowo i po stronie lewej, wielkości ok.  62x34x58mm wg PET, SUV max 5,2. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste nadprzeponowo w płucu lewym.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Odcinkowe pobudzenie metaboliczne w topografii pętli jelitowych- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nieliczne, drobne węzły chłonne krezkowe i przyaortalne, wielkości do 9x6mm.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Niewielka esowata skolioza kręgosłupa: prawowypukła w odcinku piersiowym oraz lewowypukła w odcinku piersiowym, z rotacją kręgów.  Os sacrum arcuatum. Odszczepione jądra kostnienia w okolicy spojenia łonowego obustronnie lub zmiany pourazowe.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność nadal aktywnego metabolicznie drobnego obszaru w śródpiersiu przednim pośrodkowo a także pobudzonego metabolicznie węzła chłonnego przytchawiczego - wymaga kontroli. W obecnym badaniu widoczna jest ponadto niejednorodna, częściowo rozfragmentowana masa miękkotkankowa w śródpiersiu - podejrzenie wznowy.  Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="L6" t="n">
         <v>6.1</v>
       </c>
     </row>
@@ -634,20 +784,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 94 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>: Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Znaczna hypoplazja zatok czołowych.  Klatka piersiowa i śródpiersie: Nadal utrzymuje się aktywny metabolicznie obszar w śródpiersiu przednim pośrodkowo powyżej żyły bezimiennej, wielkości  9mm wg PET SUV max do 5,2 [Im fuz. 100] oraz w topografii węzłów chłonnych przytchawiczych dolnych prawych, SUV max 4,1. Pobudzony metabolicznie węzeł chłonny przytchawiczy górny prawy wielkości 14x11mm, SUV max 4,0- do kontroli. Niejednorodnie aktywna metabolicznie masa miękkotkankowa w śródpiersiu, zamostkowo, pośrodkowo i po stronie lewej, o orientacyjnych wymiarach:.  62x23x50mm wg PET, SUV max 4,4- dokładna ocena wielkości masy mozliwa w badaniu TK KLP z kntrastem dozylnym. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste nadprzeponowo w płucu lewym.  Brzuch i miednica: Pobudzenie metaboliczne części wpustowej żołądka- czynnościowo? Odcinkowe pobudzenie metaboliczne w topografii pętli jelitowych- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Niewielka esowata skolioza kręgosłupa: prawowypukła w odcinku piersiowym oraz lewowypukła w odcinku piersiowym, z rotacją kręgów.  Os sacrum arcuatum. Odszczepione jądra kostnienia w okolicy spojenia łonowego obustronnie lub zmiany pourazowe.  Wartości referencyjne: MBPS SUVmax do 1,9; Prawy płat wątroby SUVmax do 3,3.</t>
+          <t>94</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Znaczna hypoplazja zatok czołowych.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Nadal utrzymuje się aktywny metabolicznie obszar w śródpiersiu przednim pośrodkowo powyżej żyły bezimiennej, wielkości  9mm wg PET SUV max do 5,2 [Im fuz. 100] oraz w topografii węzłów chłonnych przytchawiczych dolnych prawych, SUV max 4,1. Pobudzony metabolicznie węzeł chłonny przytchawiczy górny prawy wielkości 14x11mm, SUV max 4,0- do kontroli. Niejednorodnie aktywna metabolicznie masa miękkotkankowa w śródpiersiu, zamostkowo, pośrodkowo i po stronie lewej, o orientacyjnych wymiarach:.  62x23x50mm wg PET, SUV max 4,4- dokładna ocena wielkości masy mozliwa w badaniu TK KLP z kntrastem dozylnym. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste nadprzeponowo w płucu lewym.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne części wpustowej żołądka- czynnościowo? Odcinkowe pobudzenie metaboliczne w topografii pętli jelitowych- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Niewielka esowata skolioza kręgosłupa: prawowypukła w odcinku piersiowym oraz lewowypukła w odcinku piersiowym, z rotacją kręgów.  Os sacrum arcuatum. Odszczepione jądra kostnienia w okolicy spojenia łonowego obustronnie lub zmiany pourazowe.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność nadal aktywnego metabolicznie drobnego obszaru w śródpiersiu przednim pośrodkowo a także pobudzonego metabolicznie węzła chłonnego przytchawiczego - wymaga kontroli. Ponadto widoczna jest niejednorodna, częściowo rozfragmentowana masa miękkotkankowa w śródpiersiu - 0braz bez istotnych zmian w stosunku do badania PET z 24.07.2023.  Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="L7" t="n">
         <v>5.2</v>
       </c>
     </row>
